--- a/out/LSTM-mamba2_repeat_5_000002.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>5.448042895279977</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>5.448042895279977</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>6.048042895279977</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>6.048042895279977</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>6.048042895279977</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>6.048042895279977</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>6.048042895279977</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-mamba2_repeat_5_000002.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>5.448042895279977</v>
+        <v>2.84</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>5.448042895279977</v>
+        <v>2.84</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>6.048042895279977</v>
+        <v>2.002060435318238</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04098559548271052</v>
+        <v>0.9641208706364751</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.07381869404528718</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.07381869404528718</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6409855954827105</v>
+        <v>0.9641208706364751</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>6.048042895279977</v>
+        <v>0.9641208706364751</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04098559548271052</v>
+        <v>0.9641208706364751</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.07381869404528718</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.07381869404528718</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6409855954827105</v>
+        <v>0.764120870636475</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>6.048042895279977</v>
+        <v>2.002060435318238</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>6.048042895279977</v>
+        <v>3.04</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>6.048042895279977</v>
+        <v>2.002060435318238</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04098559548271052</v>
+        <v>0.9641208706364751</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04098559548271052</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6409855954827105</v>
+        <v>-0.2738186940452872</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-mamba2_repeat_5_000002.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.1956055760383606</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.84</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.1022270768880844</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.84</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01702533662319183</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.002060435318238</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0269041508436203</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9641208706364751</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.03794803470373154</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.07381869404528718</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.03907209634780884</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.07381869404528718</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.03865069150924683</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0300268679857254</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01615604013204575</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.02421491593122482</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.02999807894229889</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0319654643535614</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.02811655402183533</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.02859067171812057</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.03000471740961075</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.03161465376615524</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0322839692234993</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.03311344236135483</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.03455831855535507</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.03354712575674057</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.03406235575675964</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.03570318222045898</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.03593303263187408</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0168684646487236</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.02275867760181427</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.02813612669706345</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.02860752493143082</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0284264013171196</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.03062593936920166</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.03269214928150177</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0330708771944046</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.03349035233259201</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.03343555331230164</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.03287506103515625</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.02919121086597443</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.01986024528741837</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.02216096222400665</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0264112576842308</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.02025306597352028</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.01351147517561913</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.004679258912801743</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9641208706364751</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0004651844501495361</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9641208706364751</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.01560495793819427</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.9641208706364751</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.003870494663715363</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.07381869404528718</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.03058401495218277</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.07381869404528718</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.02258843928575516</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.008358847349882126</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.764120870636475</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.004271827638149261</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.002060435318238</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.007269825786352158</v>
       </c>
       <c r="JB50" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01588193327188492</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.002060435318238</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.00259699672460556</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9641208706364751</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.00957271084189415</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01186543703079224</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00847925990819931</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003553353250026703</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.007595270872116089</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.16</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.009646028280258179</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.00705903023481369</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01213482022285461</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0155918225646019</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01166479289531708</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01634617894887924</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02003681659698486</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01325833424925804</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.007675431668758392</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.005099643021821976</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01748793572187424</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02064959704875946</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01550868153572083</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01057315990328789</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009186588227748871</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01231936365365982</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01194992288947105</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0161072313785553</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02041606605052948</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02261726930737495</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02342213690280914</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02536417543888092</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02666338533163071</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02677196264266968</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02615693211555481</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02337437868118286</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02483536303043365</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02551617473363876</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02757769078016281</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0293271541595459</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02542810887098312</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02482616156339645</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.02007786184549332</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02519042789936066</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02696951478719711</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02488255500793457</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02710400521755219</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02853646129369736</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0284891203045845</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.02441006898880005</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.02670660614967346</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02920237928628922</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.03026801347732544</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02897267788648605</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.03126861155033112</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.03024046123027802</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02963858842849731</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.03121540695428848</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.03176382929086685</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.03267704695463181</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.03378888219594955</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.03363493084907532</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.03359512239694595</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.03380575031042099</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.03274986147880554</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.03331173211336136</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.03157001733779907</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.03257928043603897</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2738186940452872</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.03155358880758286</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01948218420147896</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01950613409280777</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002364598214626312</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01682303473353386</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0127730667591095</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01540671288967133</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01505888998508453</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01325751841068268</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01479466259479523</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.8599999999999997</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.007661517709493637</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2738186940452872</v>
+        <v>0.8599999999999997</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
